--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -105,7 +105,7 @@
     <t>ui</t>
   </si>
   <si>
-    <t>https://www.busonlineticket.com</t>
+    <t>https://www2.busonlineticket.com</t>
   </si>
   <si>
     <t>api</t>
@@ -169,7 +169,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,13 +198,6 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -659,148 +652,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -810,7 +803,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1332,8 +1325,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://www.busonlineticket.com"/>
-    <hyperlink ref="C15" r:id="rId1" display="https://www.busonlineticket.com"/>
+    <hyperlink ref="C14" r:id="rId1" display="https://www2.busonlineticket.com" tooltip="https://www2.busonlineticket.com"/>
+    <hyperlink ref="C15" r:id="rId1" display="https://www2.busonlineticket.com" tooltip="https://www2.busonlineticket.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TestData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TestResults" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BookingTestData" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestResults" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BookingTestData" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,11 +34,8 @@
     <font>
       <color rgb="00166534"/>
     </font>
-    <font>
-      <color rgb="00991B1B"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +52,6 @@
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,13 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -687,7 +678,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www2.busonlineticket.com</t>
+          <t>https://www.busonlineticket.com</t>
         </is>
       </c>
     </row>
@@ -704,7 +695,143 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www2.busonlineticket.com</t>
+          <t>https://www.busonlineticket.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>QA Tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0163553613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>qa.tester@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01/01/1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>passport_no</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A12345678</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>passport_expiry</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01/01/2032</t>
         </is>
       </c>
     </row>
@@ -719,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -771,17 +898,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15 17:06:00</t>
+          <t>2026-06-23 00:51:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TC-UI-01</t>
+          <t>TC-BK-00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>test_signup_full_flow</t>
+          <t>test_booking_data_available</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -795,794 +922,9 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>93.93000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TC-UI-02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>test_login_with_phone_number</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>59.63</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TC-UI-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>test_delete_signup_account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>31.68</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>20.09</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:325: in test_search_and_select_operator     assert found, ( E   AssertionError: Operator 'Transtar Travel Express' was not found in the trip results for Singapore → Genting Highlands on 30/06/2026. E     Check that the operator name in BookingTestData sheet matches the name displayed on the site exactly (partial match is used). E   assert False</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-02]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:310: in test_search_and_select_operator     WebDriverWait(driver, 20).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:121: in until     raise TimeoutException(message, screen, stacktrace) E   selenium.common.exceptions.TimeoutException: Message:  E   Stacktrace: E   	chromedriver!GetHandleVerifier [0x3fa823+10083] E   	chromedriver!GetHandleVerifier [0x3fa864+100c4] E   	chromedriver!(No symbol) [0x1da6f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-03]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:262: in test_search_and_select_operator     driver.maximize_window() ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:596: in maximize_window     self.execute(command, None) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:450: in execute     self.error_handler.check_response(response) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:06:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-04]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:265: in test_search_and_select_operator     src = driver.page_source.lower()           ^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:565: in page_source     return self.execute(Command.GET_PAGE_SOURCE)["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:450: in execute     self</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:10:58</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:157: in _pick_date     WebDriverWait(driver, 6).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:121: in until     raise TimeoutException(message, screen, stacktrace) E   selenium.common.exceptions.TimeoutException: Message:  During handling of the above exception, another exception occurred: tests\ui\test_ui_04_booking.py:350: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], dep</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:13:36</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:163: in _pick_date     WebDriverWait(driver, 6).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:121: in until     raise TimeoutException(message, screen, stacktrace) E   selenium.common.exceptions.TimeoutException: Message:  During handling of the above exception, another exception occurred: tests\ui\test_ui_04_booking.py:356: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], dep</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:16:17</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:169: in _pick_date     WebDriverWait(driver, 6).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:121: in until     raise TimeoutException(message, screen, stacktrace) E   selenium.common.exceptions.TimeoutException: Message:  During handling of the above exception, another exception occurred: tests\ui\test_ui_04_booking.py:362: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], dep</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:16:17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-02]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>25.65</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:16:17</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-03]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:332: in test_search_and_select_operator     driver.maximize_window() ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:596: in maximize_window     self.execute(command, None) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:450: in execute     self.error_handler.check_response(response) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\s</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:16:17</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-04]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:382: in test_search_and_select_operator     WebDriverWait(driver, 20).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:121: in until     raise TimeoutException(message, screen, stacktrace) E   selenium.common.exceptions.TimeoutException: Message:  E   Stacktrace: E   	chromedriver!GetHandleVerifier [0x3fa823+10083] E   	chromedriver!GetHandleVerifier [0x3fa864+100c4] E   	chromedriver!(No symbol) [0x1da6f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:19:09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:167: in _pick_date     driver.execute_script("$(arguments[0]).datepicker('show');", hidden_input) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\web</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:19:09</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-02]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:167: in _pick_date     driver.execute_script("$(arguments[0]).datepicker('show');", hidden_input) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\web</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:19:09</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-03]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:167: in _pick_date     driver.execute_script("$(arguments[0]).datepicker('show');", hidden_input) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\web</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:19:09</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-04]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:167: in _pick_date     driver.execute_script("$(arguments[0]).datepicker('show');", hidden_input) ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\web</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:22:23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:383: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], depart, ctx, label="Depart Date", tests\ui\test_ui_04_booking.py:158: in _pick_date     driver.execute_script(""" ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:22:23</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-02]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:383: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], depart, ctx, label="Depart Date", tests\ui\test_ui_04_booking.py:158: in _pick_date     driver.execute_script(""" ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:22:23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-03]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:383: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], depart, ctx, label="Depart Date", tests\ui\test_ui_04_booking.py:158: in _pick_date     driver.execute_script(""" ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:22:23</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-04]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:383: in test_search_and_select_operator     _pick_date(driver, cfg["depart_id"], depart, ctx, label="Depart Date", tests\ui\test_ui_04_booking.py:158: in _pick_date     driver.execute_script(""" ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\remote\webdriver.py:536: in execute_script     return self.execute(command, {"script": script, "args": converted_args})["value"]            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:25:42</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-01]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:420: in test_search_and_select_operator     assert found, ( E   AssertionError: Operator 'Transtar Travel Express' was not found in the trip results for Singapore → Genting Highlands on 30/06/2026. E     Check that the operator name in BookingTestData sheet matches the name displayed on the site exactly (partial match is used). E   assert False</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:25:42</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-02]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-06-15 17:25:42</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TC-BK-XX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>test_search_and_select_operator[TC-BK-03]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>tests\ui\test_ui_04_booking.py:405: in test_search_and_select_operator     WebDriverWait(driver, 20).until( ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\wait.py:112: in until     value = method(self._driver)             ^^^^^^^^^^^^^^^^^^^^ ..\..\..\AppData\Local\Programs\Python\Python311\Lib\site-packages\selenium\webdriver\support\expected_conditions.py:92: in _predicate     return driver.find_element(*locator)            ^^^^^^^^^^^^^^^^^^^^^^^</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1595,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1605,7 +947,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1646,6 +989,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Test Data (JSON)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
@@ -1683,6 +1031,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>{
+  "passengers": [
+    {
+      "first_name": "Test",
+      "last_name": "Batch Five",
+      "gender": "Male",
+      "dob": "1998-01-01",
+      "nationality": "Germany",
+      "passport_no": "A12348866",
+      "passport_expiry": "2028-04-01"
+    },
+    {
+      "first_name": "Test",
+      "last_name": "Second",
+      "gender": "Male",
+      "dob": "2006-01-01",
+      "nationality": "Malaysia",
+      "passport_no": "A12345555",
+      "passport_expiry": "2029-01-01"
+    }
+  ],
+  "depart_meal": {
+    "vegetarian": 2,
+    "non_vegetarian": 0
+  },
+  "return_meal": {
+    "vegetarian": 1,
+    "non_vegetarian": 1
+  },
+  "addons": [
+    "insurance",
+    "refund"
+  ],
+  "discount": "12.50",
+  "total": "1148.89",
+  "currency": "RM",
+  "payment_method": "Touch N Go",
+  "expected_fields": []
+}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
@@ -1690,27 +1081,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-BK-02</t>
+          <t>TC-BK-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Ferry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KTM Berhad</t>
+          <t>Bintan Resort Ferry (Economy)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KL Sentral</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Butterworth</t>
+          <t>Bintan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1719,6 +1110,43 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>{
+  "passengers": [
+    {
+      "first_name": "Test",
+      "last_name": "Batch Five",
+      "gender": "Male",
+      "dob": "2004-01-01",
+      "nationality": "Cambodia",
+      "passport_no": "A12346677",
+      "passport_expiry": "2029-01-01",
+      "country_of_issuance": "Cambodia"
+    },
+    {
+      "first_name": "Test",
+      "last_name": "Second",
+      "gender": "Male",
+      "dob": "2026-01-01",
+      "nationality": "Singapore",
+      "passport_no": "A12348324",
+      "passport_expiry": "2036-01-01",
+      "country_of_issuance": "Singapore"
+    }
+  ],
+  "child": 1,
+  "addons": [
+    "promo"
+  ],
+  "discount": "66.98",
+  "total": "646.31",
+  "currency": "RM",
+  "payment_method": "Boost",
+  "expected_fields": []
+}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1727,7 +1155,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-BK-03</t>
+          <t>TC-BK-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1737,17 +1165,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bintan Resort Ferry</t>
+          <t>Dolphin Fast Ferry</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Stulang</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bintan</t>
+          <t>Batam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1757,42 +1185,47 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC-BK-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ferry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dolphin Fast Ferry</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stulang</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Batam</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>{
+  "passengers": [
+    {
+      "first_name": "Test",
+      "last_name": "Batch Five",
+      "gender": "Male",
+      "passenger_type": "Adult",
+      "dob": "2003-04-01",
+      "nationality": "Greece",
+      "passport_no": "A12349976",
+      "passport_issue": "2020-04-01",
+      "passport_expiry": "2028-04-01",
+      "country_of_issuance": "Greece"
+    },
+    {
+      "first_name": "Test",
+      "last_name": "Second",
+      "gender": "Male",
+      "passenger_type": "Child",
+      "dob": "2025-01-01",
+      "nationality": "Singapore",
+      "passport_no": "A12346636",
+      "passport_issue": "2026-04-01",
+      "passport_expiry": "2026-07-01",
+      "country_of_issuance": "Singapore"
+    }
+  ],
+  "child": 1,
+  "addons": [
+    "refund",
+    "promo"
+  ],
+  "discount": "2.00",
+  "total": "110.70",
+  "currency": "SGD",
+  "payment_method": "PayNow",
+  "expected_fields": []
+}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
